--- a/260921_construction-period-review/demo/sample-boq.xlsx
+++ b/260921_construction-period-review/demo/sample-boq.xlsx
@@ -471,9 +471,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -546,7 +543,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1850</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +571,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3240</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="7">
@@ -666,7 +663,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2900</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="11">
@@ -814,7 +811,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3960</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +835,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
